--- a/public/assets/templates/operasional/mdp.xlsx
+++ b/public/assets/templates/operasional/mdp.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ThinkPad\Documents\MAGANG\PT BAS\ENG\Operasional\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\pt_bas\Engineering\public\assets\templates\operasional\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D062CBD-2B71-4A0D-897E-4F88AF3F3839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98D5229B-A533-40B3-80D8-59FD83500C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{48748F47-9D71-4608-BC1F-023F595FFB4F}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>PT BUMI ALAM SEGAR</t>
   </si>
@@ -109,6 +109,15 @@
   </si>
   <si>
     <t>FORM/EUT/01/003-00</t>
+  </si>
+  <si>
+    <t>Suhu Ruang</t>
+  </si>
+  <si>
+    <t>Trafo</t>
+  </si>
+  <si>
+    <t>Genset</t>
   </si>
 </sst>
 </file>
@@ -471,18 +480,6 @@
   </cellStyleXfs>
   <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -507,89 +504,101 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -954,900 +963,979 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA62DEA-D2A8-447E-A1F9-1EDAF0B4AA94}">
-  <dimension ref="A1:S36"/>
+  <dimension ref="A1:U36"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:19" ht="15" thickTop="1">
-      <c r="A1" s="1"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="3" t="s">
+    <row r="1" spans="1:21" ht="15" thickTop="1">
+      <c r="A1" s="31"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="5" t="s">
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="36"/>
+      <c r="O1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="7"/>
-      <c r="S1" s="8"/>
-    </row>
-    <row r="2" spans="1:19">
-      <c r="A2" s="9"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="11" t="s">
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="4"/>
+    </row>
+    <row r="2" spans="1:21">
+      <c r="A2" s="33"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="12"/>
-      <c r="O2" s="13" t="s">
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
+      <c r="N2" s="38"/>
+      <c r="O2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="P2" s="14"/>
-      <c r="Q2" s="14"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="16"/>
-    </row>
-    <row r="3" spans="1:19">
-      <c r="A3" s="17" t="s">
+      <c r="P2" s="8"/>
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8"/>
+      <c r="S2" s="8"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="10"/>
+    </row>
+    <row r="3" spans="1:21">
+      <c r="A3" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="E3" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="21"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="19" t="s">
+      <c r="F3" s="24"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="20" t="s">
+      <c r="I3" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="21"/>
-      <c r="K3" s="22"/>
-      <c r="L3" s="19" t="s">
+      <c r="J3" s="24"/>
+      <c r="K3" s="30"/>
+      <c r="L3" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="20" t="s">
+      <c r="M3" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="N3" s="21"/>
-      <c r="O3" s="21"/>
-      <c r="P3" s="23" t="s">
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="23"/>
-      <c r="R3" s="18" t="s">
+      <c r="Q3" s="25"/>
+      <c r="R3" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="S3" s="25"/>
+      <c r="T3" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="S3" s="24" t="s">
+      <c r="U3" s="28" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="26">
-      <c r="A4" s="25"/>
-      <c r="B4" s="26"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="28" t="s">
+    <row r="4" spans="1:21" ht="26">
+      <c r="A4" s="40"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="28" t="s">
+      <c r="G4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="27"/>
-      <c r="I4" s="28" t="s">
+      <c r="H4" s="22"/>
+      <c r="I4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="28" t="s">
+      <c r="J4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="K4" s="28" t="s">
+      <c r="K4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="L4" s="27"/>
-      <c r="M4" s="28" t="s">
+      <c r="L4" s="22"/>
+      <c r="M4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N4" s="28" t="s">
+      <c r="N4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="O4" s="13" t="s">
+      <c r="O4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="P4" s="29" t="s">
+      <c r="P4" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="Q4" s="28" t="s">
+      <c r="Q4" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="R4" s="26"/>
-      <c r="S4" s="30"/>
-    </row>
-    <row r="5" spans="1:19">
-      <c r="A5" s="31">
+      <c r="R4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S4" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="T4" s="27"/>
+      <c r="U4" s="29"/>
+    </row>
+    <row r="5" spans="1:21">
+      <c r="A5" s="5">
         <v>1</v>
       </c>
-      <c r="B5" s="28"/>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
-      <c r="F5" s="32"/>
-      <c r="G5" s="32"/>
-      <c r="H5" s="32"/>
-      <c r="I5" s="32"/>
-      <c r="J5" s="32"/>
-      <c r="K5" s="32"/>
-      <c r="L5" s="32"/>
-      <c r="M5" s="32"/>
-      <c r="N5" s="32"/>
-      <c r="O5" s="33"/>
-      <c r="P5" s="33"/>
-      <c r="Q5" s="33"/>
-      <c r="R5" s="32"/>
-      <c r="S5" s="34"/>
-    </row>
-    <row r="6" spans="1:19">
-      <c r="A6" s="31">
+      <c r="B5" s="6"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13"/>
+      <c r="S5" s="13"/>
+      <c r="T5" s="12"/>
+      <c r="U5" s="14"/>
+    </row>
+    <row r="6" spans="1:21">
+      <c r="A6" s="5">
         <v>2</v>
       </c>
-      <c r="B6" s="28"/>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="32"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="32"/>
-      <c r="I6" s="32"/>
-      <c r="J6" s="32"/>
-      <c r="K6" s="32"/>
-      <c r="L6" s="32"/>
-      <c r="M6" s="32"/>
-      <c r="N6" s="32"/>
-      <c r="O6" s="33"/>
-      <c r="P6" s="33"/>
-      <c r="Q6" s="33"/>
-      <c r="R6" s="32"/>
-      <c r="S6" s="34"/>
-    </row>
-    <row r="7" spans="1:19">
-      <c r="A7" s="31">
+      <c r="B6" s="6"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="12"/>
+      <c r="O6" s="13"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="13"/>
+      <c r="S6" s="13"/>
+      <c r="T6" s="12"/>
+      <c r="U6" s="14"/>
+    </row>
+    <row r="7" spans="1:21">
+      <c r="A7" s="5">
         <v>3</v>
       </c>
-      <c r="B7" s="28"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32"/>
-      <c r="I7" s="32"/>
-      <c r="J7" s="32"/>
-      <c r="K7" s="32"/>
-      <c r="L7" s="32"/>
-      <c r="M7" s="32"/>
-      <c r="N7" s="32"/>
-      <c r="O7" s="33"/>
-      <c r="P7" s="33"/>
-      <c r="Q7" s="33"/>
-      <c r="R7" s="32"/>
-      <c r="S7" s="34"/>
-    </row>
-    <row r="8" spans="1:19">
-      <c r="A8" s="31">
+      <c r="B7" s="6"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="13"/>
+      <c r="S7" s="13"/>
+      <c r="T7" s="12"/>
+      <c r="U7" s="14"/>
+    </row>
+    <row r="8" spans="1:21">
+      <c r="A8" s="5">
         <v>4</v>
       </c>
-      <c r="B8" s="28"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
-      <c r="K8" s="32"/>
-      <c r="L8" s="32"/>
-      <c r="M8" s="32"/>
-      <c r="N8" s="32"/>
-      <c r="O8" s="33"/>
-      <c r="P8" s="33"/>
-      <c r="Q8" s="33"/>
-      <c r="R8" s="32"/>
-      <c r="S8" s="34"/>
-    </row>
-    <row r="9" spans="1:19">
-      <c r="A9" s="31">
+      <c r="B8" s="6"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="13"/>
+      <c r="S8" s="13"/>
+      <c r="T8" s="12"/>
+      <c r="U8" s="14"/>
+    </row>
+    <row r="9" spans="1:21">
+      <c r="A9" s="5">
         <v>5</v>
       </c>
-      <c r="B9" s="28"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
-      <c r="K9" s="32"/>
-      <c r="L9" s="32"/>
-      <c r="M9" s="32"/>
-      <c r="N9" s="32"/>
-      <c r="O9" s="33"/>
-      <c r="P9" s="33"/>
-      <c r="Q9" s="33"/>
-      <c r="R9" s="32"/>
-      <c r="S9" s="34"/>
-    </row>
-    <row r="10" spans="1:19">
-      <c r="A10" s="31">
+      <c r="B9" s="6"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="13"/>
+      <c r="S9" s="13"/>
+      <c r="T9" s="12"/>
+      <c r="U9" s="14"/>
+    </row>
+    <row r="10" spans="1:21">
+      <c r="A10" s="5">
         <v>6</v>
       </c>
-      <c r="B10" s="28"/>
-      <c r="C10" s="32"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
-      <c r="K10" s="32"/>
-      <c r="L10" s="32"/>
-      <c r="M10" s="32"/>
-      <c r="N10" s="32"/>
-      <c r="O10" s="33"/>
-      <c r="P10" s="33"/>
-      <c r="Q10" s="33"/>
-      <c r="R10" s="32"/>
-      <c r="S10" s="34"/>
-    </row>
-    <row r="11" spans="1:19">
-      <c r="A11" s="31">
+      <c r="B10" s="6"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
+      <c r="S10" s="13"/>
+      <c r="T10" s="12"/>
+      <c r="U10" s="14"/>
+    </row>
+    <row r="11" spans="1:21">
+      <c r="A11" s="5">
         <v>7</v>
       </c>
-      <c r="B11" s="28"/>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
-      <c r="K11" s="32"/>
-      <c r="L11" s="32"/>
-      <c r="M11" s="32"/>
-      <c r="N11" s="32"/>
-      <c r="O11" s="33"/>
-      <c r="P11" s="33"/>
-      <c r="Q11" s="33"/>
-      <c r="R11" s="32"/>
-      <c r="S11" s="34"/>
-    </row>
-    <row r="12" spans="1:19">
-      <c r="A12" s="31">
+      <c r="B11" s="6"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="13"/>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="13"/>
+      <c r="R11" s="13"/>
+      <c r="S11" s="13"/>
+      <c r="T11" s="12"/>
+      <c r="U11" s="14"/>
+    </row>
+    <row r="12" spans="1:21">
+      <c r="A12" s="5">
         <v>8</v>
       </c>
-      <c r="B12" s="28"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="32"/>
-      <c r="K12" s="32"/>
-      <c r="L12" s="32"/>
-      <c r="M12" s="32"/>
-      <c r="N12" s="32"/>
-      <c r="O12" s="33"/>
-      <c r="P12" s="33"/>
-      <c r="Q12" s="33"/>
-      <c r="R12" s="32"/>
-      <c r="S12" s="34"/>
-    </row>
-    <row r="13" spans="1:19">
-      <c r="A13" s="31">
+      <c r="B12" s="6"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="13"/>
+      <c r="P12" s="13"/>
+      <c r="Q12" s="13"/>
+      <c r="R12" s="13"/>
+      <c r="S12" s="13"/>
+      <c r="T12" s="12"/>
+      <c r="U12" s="14"/>
+    </row>
+    <row r="13" spans="1:21">
+      <c r="A13" s="5">
         <v>9</v>
       </c>
-      <c r="B13" s="28"/>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="32"/>
-      <c r="J13" s="32"/>
-      <c r="K13" s="32"/>
-      <c r="L13" s="32"/>
-      <c r="M13" s="32"/>
-      <c r="N13" s="32"/>
-      <c r="O13" s="33"/>
-      <c r="P13" s="33"/>
-      <c r="Q13" s="33"/>
-      <c r="R13" s="32"/>
-      <c r="S13" s="34"/>
-    </row>
-    <row r="14" spans="1:19">
-      <c r="A14" s="31">
+      <c r="B13" s="6"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="13"/>
+      <c r="P13" s="13"/>
+      <c r="Q13" s="13"/>
+      <c r="R13" s="13"/>
+      <c r="S13" s="13"/>
+      <c r="T13" s="12"/>
+      <c r="U13" s="14"/>
+    </row>
+    <row r="14" spans="1:21">
+      <c r="A14" s="5">
         <v>10</v>
       </c>
-      <c r="B14" s="28"/>
-      <c r="C14" s="32"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="32"/>
-      <c r="J14" s="32"/>
-      <c r="K14" s="32"/>
-      <c r="L14" s="32"/>
-      <c r="M14" s="32"/>
-      <c r="N14" s="32"/>
-      <c r="O14" s="33"/>
-      <c r="P14" s="33"/>
-      <c r="Q14" s="33"/>
-      <c r="R14" s="32"/>
-      <c r="S14" s="34"/>
-    </row>
-    <row r="15" spans="1:19">
-      <c r="A15" s="31">
+      <c r="B14" s="6"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="13"/>
+      <c r="P14" s="13"/>
+      <c r="Q14" s="13"/>
+      <c r="R14" s="13"/>
+      <c r="S14" s="13"/>
+      <c r="T14" s="12"/>
+      <c r="U14" s="14"/>
+    </row>
+    <row r="15" spans="1:21">
+      <c r="A15" s="5">
         <v>11</v>
       </c>
-      <c r="B15" s="28"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="32"/>
-      <c r="K15" s="32"/>
-      <c r="L15" s="32"/>
-      <c r="M15" s="32"/>
-      <c r="N15" s="32"/>
-      <c r="O15" s="33"/>
-      <c r="P15" s="33"/>
-      <c r="Q15" s="33"/>
-      <c r="R15" s="32"/>
-      <c r="S15" s="34"/>
-    </row>
-    <row r="16" spans="1:19">
-      <c r="A16" s="31">
+      <c r="B15" s="6"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="13"/>
+      <c r="P15" s="13"/>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13"/>
+      <c r="S15" s="13"/>
+      <c r="T15" s="12"/>
+      <c r="U15" s="14"/>
+    </row>
+    <row r="16" spans="1:21">
+      <c r="A16" s="5">
         <v>12</v>
       </c>
-      <c r="B16" s="28"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="32"/>
-      <c r="K16" s="32"/>
-      <c r="L16" s="32"/>
-      <c r="M16" s="32"/>
-      <c r="N16" s="32"/>
-      <c r="O16" s="33"/>
-      <c r="P16" s="33"/>
-      <c r="Q16" s="33"/>
-      <c r="R16" s="32"/>
-      <c r="S16" s="34"/>
-    </row>
-    <row r="17" spans="1:19">
-      <c r="A17" s="31">
+      <c r="B16" s="6"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="12"/>
+      <c r="O16" s="13"/>
+      <c r="P16" s="13"/>
+      <c r="Q16" s="13"/>
+      <c r="R16" s="13"/>
+      <c r="S16" s="13"/>
+      <c r="T16" s="12"/>
+      <c r="U16" s="14"/>
+    </row>
+    <row r="17" spans="1:21">
+      <c r="A17" s="5">
         <v>13</v>
       </c>
-      <c r="B17" s="28"/>
-      <c r="C17" s="32"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="32"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="32"/>
-      <c r="K17" s="32"/>
-      <c r="L17" s="32"/>
-      <c r="M17" s="32"/>
-      <c r="N17" s="32"/>
-      <c r="O17" s="33"/>
-      <c r="P17" s="33"/>
-      <c r="Q17" s="33"/>
-      <c r="R17" s="32"/>
-      <c r="S17" s="34"/>
-    </row>
-    <row r="18" spans="1:19">
-      <c r="A18" s="31">
+      <c r="B17" s="6"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="12"/>
+      <c r="O17" s="13"/>
+      <c r="P17" s="13"/>
+      <c r="Q17" s="13"/>
+      <c r="R17" s="13"/>
+      <c r="S17" s="13"/>
+      <c r="T17" s="12"/>
+      <c r="U17" s="14"/>
+    </row>
+    <row r="18" spans="1:21">
+      <c r="A18" s="5">
         <v>14</v>
       </c>
-      <c r="B18" s="28"/>
-      <c r="C18" s="32"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="32"/>
-      <c r="K18" s="32"/>
-      <c r="L18" s="32"/>
-      <c r="M18" s="32"/>
-      <c r="N18" s="32"/>
-      <c r="O18" s="33"/>
-      <c r="P18" s="33"/>
-      <c r="Q18" s="33"/>
-      <c r="R18" s="32"/>
-      <c r="S18" s="34"/>
-    </row>
-    <row r="19" spans="1:19">
-      <c r="A19" s="31">
+      <c r="B18" s="6"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="13"/>
+      <c r="P18" s="13"/>
+      <c r="Q18" s="13"/>
+      <c r="R18" s="13"/>
+      <c r="S18" s="13"/>
+      <c r="T18" s="12"/>
+      <c r="U18" s="14"/>
+    </row>
+    <row r="19" spans="1:21">
+      <c r="A19" s="5">
         <v>15</v>
       </c>
-      <c r="B19" s="28"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="32"/>
-      <c r="J19" s="32"/>
-      <c r="K19" s="32"/>
-      <c r="L19" s="32"/>
-      <c r="M19" s="32"/>
-      <c r="N19" s="32"/>
-      <c r="O19" s="33"/>
-      <c r="P19" s="33"/>
-      <c r="Q19" s="33"/>
-      <c r="R19" s="32"/>
-      <c r="S19" s="34"/>
-    </row>
-    <row r="20" spans="1:19">
-      <c r="A20" s="31">
+      <c r="B19" s="6"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="12"/>
+      <c r="N19" s="12"/>
+      <c r="O19" s="13"/>
+      <c r="P19" s="13"/>
+      <c r="Q19" s="13"/>
+      <c r="R19" s="13"/>
+      <c r="S19" s="13"/>
+      <c r="T19" s="12"/>
+      <c r="U19" s="14"/>
+    </row>
+    <row r="20" spans="1:21">
+      <c r="A20" s="5">
         <v>16</v>
       </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="32"/>
-      <c r="I20" s="32"/>
-      <c r="J20" s="32"/>
-      <c r="K20" s="32"/>
-      <c r="L20" s="32"/>
-      <c r="M20" s="32"/>
-      <c r="N20" s="32"/>
-      <c r="O20" s="33"/>
-      <c r="P20" s="33"/>
-      <c r="Q20" s="33"/>
-      <c r="R20" s="32"/>
-      <c r="S20" s="34"/>
-    </row>
-    <row r="21" spans="1:19">
-      <c r="A21" s="31">
+      <c r="B20" s="6"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="12"/>
+      <c r="N20" s="12"/>
+      <c r="O20" s="13"/>
+      <c r="P20" s="13"/>
+      <c r="Q20" s="13"/>
+      <c r="R20" s="13"/>
+      <c r="S20" s="13"/>
+      <c r="T20" s="12"/>
+      <c r="U20" s="14"/>
+    </row>
+    <row r="21" spans="1:21">
+      <c r="A21" s="5">
         <v>17</v>
       </c>
-      <c r="B21" s="28"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
-      <c r="L21" s="32"/>
-      <c r="M21" s="32"/>
-      <c r="N21" s="32"/>
-      <c r="O21" s="33"/>
-      <c r="P21" s="33"/>
-      <c r="Q21" s="33"/>
-      <c r="R21" s="32"/>
-      <c r="S21" s="34"/>
-    </row>
-    <row r="22" spans="1:19">
-      <c r="A22" s="31">
+      <c r="B21" s="6"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="12"/>
+      <c r="N21" s="12"/>
+      <c r="O21" s="13"/>
+      <c r="P21" s="13"/>
+      <c r="Q21" s="13"/>
+      <c r="R21" s="13"/>
+      <c r="S21" s="13"/>
+      <c r="T21" s="12"/>
+      <c r="U21" s="14"/>
+    </row>
+    <row r="22" spans="1:21">
+      <c r="A22" s="5">
         <v>18</v>
       </c>
-      <c r="B22" s="28"/>
-      <c r="C22" s="32"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="32"/>
-      <c r="I22" s="32"/>
-      <c r="J22" s="32"/>
-      <c r="K22" s="32"/>
-      <c r="L22" s="32"/>
-      <c r="M22" s="32"/>
-      <c r="N22" s="32"/>
-      <c r="O22" s="33"/>
-      <c r="P22" s="33"/>
-      <c r="Q22" s="33"/>
-      <c r="R22" s="32"/>
-      <c r="S22" s="34"/>
-    </row>
-    <row r="23" spans="1:19">
-      <c r="A23" s="31">
+      <c r="B22" s="6"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
+      <c r="L22" s="12"/>
+      <c r="M22" s="12"/>
+      <c r="N22" s="12"/>
+      <c r="O22" s="13"/>
+      <c r="P22" s="13"/>
+      <c r="Q22" s="13"/>
+      <c r="R22" s="13"/>
+      <c r="S22" s="13"/>
+      <c r="T22" s="12"/>
+      <c r="U22" s="14"/>
+    </row>
+    <row r="23" spans="1:21">
+      <c r="A23" s="5">
         <v>19</v>
       </c>
-      <c r="B23" s="28"/>
-      <c r="C23" s="32"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="32"/>
-      <c r="I23" s="32"/>
-      <c r="J23" s="32"/>
-      <c r="K23" s="32"/>
-      <c r="L23" s="32"/>
-      <c r="M23" s="32"/>
-      <c r="N23" s="32"/>
-      <c r="O23" s="33"/>
-      <c r="P23" s="33"/>
-      <c r="Q23" s="33"/>
-      <c r="R23" s="32"/>
-      <c r="S23" s="34"/>
-    </row>
-    <row r="24" spans="1:19">
-      <c r="A24" s="31">
+      <c r="B23" s="6"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="12"/>
+      <c r="M23" s="12"/>
+      <c r="N23" s="12"/>
+      <c r="O23" s="13"/>
+      <c r="P23" s="13"/>
+      <c r="Q23" s="13"/>
+      <c r="R23" s="13"/>
+      <c r="S23" s="13"/>
+      <c r="T23" s="12"/>
+      <c r="U23" s="14"/>
+    </row>
+    <row r="24" spans="1:21">
+      <c r="A24" s="5">
         <v>20</v>
       </c>
-      <c r="B24" s="28"/>
-      <c r="C24" s="32"/>
-      <c r="D24" s="32"/>
-      <c r="E24" s="32"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="32"/>
-      <c r="I24" s="32"/>
-      <c r="J24" s="32"/>
-      <c r="K24" s="32"/>
-      <c r="L24" s="32"/>
-      <c r="M24" s="32"/>
-      <c r="N24" s="32"/>
-      <c r="O24" s="33"/>
-      <c r="P24" s="33"/>
-      <c r="Q24" s="33"/>
-      <c r="R24" s="32"/>
-      <c r="S24" s="34"/>
-    </row>
-    <row r="25" spans="1:19">
-      <c r="A25" s="31">
+      <c r="B24" s="6"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="12"/>
+      <c r="M24" s="12"/>
+      <c r="N24" s="12"/>
+      <c r="O24" s="13"/>
+      <c r="P24" s="13"/>
+      <c r="Q24" s="13"/>
+      <c r="R24" s="13"/>
+      <c r="S24" s="13"/>
+      <c r="T24" s="12"/>
+      <c r="U24" s="14"/>
+    </row>
+    <row r="25" spans="1:21">
+      <c r="A25" s="5">
         <v>21</v>
       </c>
-      <c r="B25" s="28"/>
-      <c r="C25" s="32"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="32"/>
-      <c r="J25" s="32"/>
-      <c r="K25" s="32"/>
-      <c r="L25" s="32"/>
-      <c r="M25" s="32"/>
-      <c r="N25" s="32"/>
-      <c r="O25" s="33"/>
-      <c r="P25" s="33"/>
-      <c r="Q25" s="33"/>
-      <c r="R25" s="32"/>
-      <c r="S25" s="34"/>
-    </row>
-    <row r="26" spans="1:19">
-      <c r="A26" s="31">
+      <c r="B25" s="6"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="12"/>
+      <c r="L25" s="12"/>
+      <c r="M25" s="12"/>
+      <c r="N25" s="12"/>
+      <c r="O25" s="13"/>
+      <c r="P25" s="13"/>
+      <c r="Q25" s="13"/>
+      <c r="R25" s="13"/>
+      <c r="S25" s="13"/>
+      <c r="T25" s="12"/>
+      <c r="U25" s="14"/>
+    </row>
+    <row r="26" spans="1:21">
+      <c r="A26" s="5">
         <v>22</v>
       </c>
-      <c r="B26" s="28"/>
-      <c r="C26" s="32"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="32"/>
-      <c r="K26" s="32"/>
-      <c r="L26" s="32"/>
-      <c r="M26" s="32"/>
-      <c r="N26" s="32"/>
-      <c r="O26" s="33"/>
-      <c r="P26" s="33"/>
-      <c r="Q26" s="33"/>
-      <c r="R26" s="32"/>
-      <c r="S26" s="34"/>
-    </row>
-    <row r="27" spans="1:19">
-      <c r="A27" s="31">
+      <c r="B26" s="6"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
+      <c r="L26" s="12"/>
+      <c r="M26" s="12"/>
+      <c r="N26" s="12"/>
+      <c r="O26" s="13"/>
+      <c r="P26" s="13"/>
+      <c r="Q26" s="13"/>
+      <c r="R26" s="13"/>
+      <c r="S26" s="13"/>
+      <c r="T26" s="12"/>
+      <c r="U26" s="14"/>
+    </row>
+    <row r="27" spans="1:21">
+      <c r="A27" s="5">
         <v>23</v>
       </c>
-      <c r="B27" s="28"/>
-      <c r="C27" s="32"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="32"/>
-      <c r="I27" s="32"/>
-      <c r="J27" s="32"/>
-      <c r="K27" s="32"/>
-      <c r="L27" s="32"/>
-      <c r="M27" s="32"/>
-      <c r="N27" s="32"/>
-      <c r="O27" s="33"/>
-      <c r="P27" s="33"/>
-      <c r="Q27" s="33"/>
-      <c r="R27" s="32"/>
-      <c r="S27" s="34"/>
-    </row>
-    <row r="28" spans="1:19">
-      <c r="A28" s="31">
+      <c r="B27" s="6"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12"/>
+      <c r="L27" s="12"/>
+      <c r="M27" s="12"/>
+      <c r="N27" s="12"/>
+      <c r="O27" s="13"/>
+      <c r="P27" s="13"/>
+      <c r="Q27" s="13"/>
+      <c r="R27" s="13"/>
+      <c r="S27" s="13"/>
+      <c r="T27" s="12"/>
+      <c r="U27" s="14"/>
+    </row>
+    <row r="28" spans="1:21">
+      <c r="A28" s="5">
         <v>24</v>
       </c>
-      <c r="B28" s="28"/>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="H28" s="32"/>
-      <c r="I28" s="32"/>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="32"/>
-      <c r="O28" s="33"/>
-      <c r="P28" s="33"/>
-      <c r="Q28" s="33"/>
-      <c r="R28" s="32"/>
-      <c r="S28" s="34"/>
-    </row>
-    <row r="29" spans="1:19">
-      <c r="A29" s="31">
+      <c r="B28" s="6"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="12"/>
+      <c r="L28" s="12"/>
+      <c r="M28" s="12"/>
+      <c r="N28" s="12"/>
+      <c r="O28" s="13"/>
+      <c r="P28" s="13"/>
+      <c r="Q28" s="13"/>
+      <c r="R28" s="13"/>
+      <c r="S28" s="13"/>
+      <c r="T28" s="12"/>
+      <c r="U28" s="14"/>
+    </row>
+    <row r="29" spans="1:21">
+      <c r="A29" s="5">
         <v>25</v>
       </c>
-      <c r="B29" s="28"/>
-      <c r="C29" s="32"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="32"/>
-      <c r="H29" s="32"/>
-      <c r="I29" s="32"/>
-      <c r="J29" s="32"/>
-      <c r="K29" s="32"/>
-      <c r="L29" s="32"/>
-      <c r="M29" s="32"/>
-      <c r="N29" s="32"/>
-      <c r="O29" s="33"/>
-      <c r="P29" s="33"/>
-      <c r="Q29" s="33"/>
-      <c r="R29" s="32"/>
-      <c r="S29" s="34"/>
-    </row>
-    <row r="30" spans="1:19">
-      <c r="A30" s="31">
+      <c r="B29" s="6"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="12"/>
+      <c r="M29" s="12"/>
+      <c r="N29" s="12"/>
+      <c r="O29" s="13"/>
+      <c r="P29" s="13"/>
+      <c r="Q29" s="13"/>
+      <c r="R29" s="13"/>
+      <c r="S29" s="13"/>
+      <c r="T29" s="12"/>
+      <c r="U29" s="14"/>
+    </row>
+    <row r="30" spans="1:21">
+      <c r="A30" s="5">
         <v>26</v>
       </c>
-      <c r="B30" s="28"/>
-      <c r="C30" s="32"/>
-      <c r="D30" s="32"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="32"/>
-      <c r="H30" s="32"/>
-      <c r="I30" s="32"/>
-      <c r="J30" s="32"/>
-      <c r="K30" s="32"/>
-      <c r="L30" s="32"/>
-      <c r="M30" s="32"/>
-      <c r="N30" s="32"/>
-      <c r="O30" s="33"/>
-      <c r="P30" s="33"/>
-      <c r="Q30" s="33"/>
-      <c r="R30" s="32"/>
-      <c r="S30" s="34"/>
-    </row>
-    <row r="31" spans="1:19">
-      <c r="A31" s="31">
+      <c r="B30" s="6"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="12"/>
+      <c r="L30" s="12"/>
+      <c r="M30" s="12"/>
+      <c r="N30" s="12"/>
+      <c r="O30" s="13"/>
+      <c r="P30" s="13"/>
+      <c r="Q30" s="13"/>
+      <c r="R30" s="13"/>
+      <c r="S30" s="13"/>
+      <c r="T30" s="12"/>
+      <c r="U30" s="14"/>
+    </row>
+    <row r="31" spans="1:21">
+      <c r="A31" s="5">
         <v>27</v>
       </c>
-      <c r="B31" s="28"/>
-      <c r="C31" s="32"/>
-      <c r="D31" s="32"/>
-      <c r="E31" s="32"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="32"/>
-      <c r="H31" s="32"/>
-      <c r="I31" s="32"/>
-      <c r="J31" s="32"/>
-      <c r="K31" s="32"/>
-      <c r="L31" s="32"/>
-      <c r="M31" s="32"/>
-      <c r="N31" s="32"/>
-      <c r="O31" s="33"/>
-      <c r="P31" s="33"/>
-      <c r="Q31" s="33"/>
-      <c r="R31" s="32"/>
-      <c r="S31" s="34"/>
-    </row>
-    <row r="32" spans="1:19">
-      <c r="A32" s="31">
+      <c r="B31" s="6"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="12"/>
+      <c r="L31" s="12"/>
+      <c r="M31" s="12"/>
+      <c r="N31" s="12"/>
+      <c r="O31" s="13"/>
+      <c r="P31" s="13"/>
+      <c r="Q31" s="13"/>
+      <c r="R31" s="13"/>
+      <c r="S31" s="13"/>
+      <c r="T31" s="12"/>
+      <c r="U31" s="14"/>
+    </row>
+    <row r="32" spans="1:21">
+      <c r="A32" s="5">
         <v>28</v>
       </c>
-      <c r="B32" s="28"/>
-      <c r="C32" s="32"/>
-      <c r="D32" s="32"/>
-      <c r="E32" s="32"/>
-      <c r="F32" s="32"/>
-      <c r="G32" s="32"/>
-      <c r="H32" s="32"/>
-      <c r="I32" s="32"/>
-      <c r="J32" s="32"/>
-      <c r="K32" s="32"/>
-      <c r="L32" s="32"/>
-      <c r="M32" s="32"/>
-      <c r="N32" s="32"/>
-      <c r="O32" s="33"/>
-      <c r="P32" s="33"/>
-      <c r="Q32" s="33"/>
-      <c r="R32" s="32"/>
-      <c r="S32" s="34"/>
-    </row>
-    <row r="33" spans="1:19">
-      <c r="A33" s="31">
+      <c r="B32" s="6"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="12"/>
+      <c r="M32" s="12"/>
+      <c r="N32" s="12"/>
+      <c r="O32" s="13"/>
+      <c r="P32" s="13"/>
+      <c r="Q32" s="13"/>
+      <c r="R32" s="13"/>
+      <c r="S32" s="13"/>
+      <c r="T32" s="12"/>
+      <c r="U32" s="14"/>
+    </row>
+    <row r="33" spans="1:21">
+      <c r="A33" s="5">
         <v>29</v>
       </c>
-      <c r="B33" s="28"/>
-      <c r="C33" s="32"/>
-      <c r="D33" s="32"/>
-      <c r="E33" s="32"/>
-      <c r="F33" s="32"/>
-      <c r="G33" s="32"/>
-      <c r="H33" s="32"/>
-      <c r="I33" s="32"/>
-      <c r="J33" s="32"/>
-      <c r="K33" s="32"/>
-      <c r="L33" s="32"/>
-      <c r="M33" s="32"/>
-      <c r="N33" s="32"/>
-      <c r="O33" s="33"/>
-      <c r="P33" s="33"/>
-      <c r="Q33" s="33"/>
-      <c r="R33" s="32"/>
-      <c r="S33" s="34"/>
-    </row>
-    <row r="34" spans="1:19">
-      <c r="A34" s="31">
+      <c r="B33" s="6"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="12"/>
+      <c r="K33" s="12"/>
+      <c r="L33" s="12"/>
+      <c r="M33" s="12"/>
+      <c r="N33" s="12"/>
+      <c r="O33" s="13"/>
+      <c r="P33" s="13"/>
+      <c r="Q33" s="13"/>
+      <c r="R33" s="13"/>
+      <c r="S33" s="13"/>
+      <c r="T33" s="12"/>
+      <c r="U33" s="14"/>
+    </row>
+    <row r="34" spans="1:21">
+      <c r="A34" s="5">
         <v>30</v>
       </c>
-      <c r="B34" s="28"/>
-      <c r="C34" s="32"/>
-      <c r="D34" s="32"/>
-      <c r="E34" s="32"/>
-      <c r="F34" s="32"/>
-      <c r="G34" s="32"/>
-      <c r="H34" s="32"/>
-      <c r="I34" s="32"/>
-      <c r="J34" s="32"/>
-      <c r="K34" s="32"/>
-      <c r="L34" s="32"/>
-      <c r="M34" s="32"/>
-      <c r="N34" s="32"/>
-      <c r="O34" s="33"/>
-      <c r="P34" s="33"/>
-      <c r="Q34" s="33"/>
-      <c r="R34" s="32"/>
-      <c r="S34" s="34"/>
-    </row>
-    <row r="35" spans="1:19" ht="15" thickBot="1">
-      <c r="A35" s="35">
+      <c r="B34" s="6"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="12"/>
+      <c r="K34" s="12"/>
+      <c r="L34" s="12"/>
+      <c r="M34" s="12"/>
+      <c r="N34" s="12"/>
+      <c r="O34" s="13"/>
+      <c r="P34" s="13"/>
+      <c r="Q34" s="13"/>
+      <c r="R34" s="13"/>
+      <c r="S34" s="13"/>
+      <c r="T34" s="12"/>
+      <c r="U34" s="14"/>
+    </row>
+    <row r="35" spans="1:21" ht="15" thickBot="1">
+      <c r="A35" s="15">
         <v>31</v>
       </c>
-      <c r="B35" s="36"/>
-      <c r="C35" s="36"/>
-      <c r="D35" s="36"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="36"/>
-      <c r="G35" s="36"/>
-      <c r="H35" s="36"/>
-      <c r="I35" s="36"/>
-      <c r="J35" s="36"/>
-      <c r="K35" s="36"/>
-      <c r="L35" s="36"/>
-      <c r="M35" s="36"/>
-      <c r="N35" s="36"/>
-      <c r="O35" s="37"/>
-      <c r="P35" s="37"/>
-      <c r="Q35" s="37"/>
-      <c r="R35" s="36"/>
-      <c r="S35" s="38"/>
-    </row>
-    <row r="36" spans="1:19" ht="15" thickTop="1">
-      <c r="A36" s="39"/>
-      <c r="B36" s="39"/>
-      <c r="C36" s="39"/>
-      <c r="D36" s="39"/>
-      <c r="E36" s="39"/>
-      <c r="F36" s="39"/>
-      <c r="G36" s="39"/>
-      <c r="H36" s="39"/>
-      <c r="I36" s="39"/>
-      <c r="J36" s="39"/>
-      <c r="K36" s="39"/>
-      <c r="L36" s="39"/>
-      <c r="M36" s="39"/>
-      <c r="N36" s="39"/>
-      <c r="O36" s="39"/>
-      <c r="P36" s="39"/>
-      <c r="Q36" s="39"/>
-      <c r="R36" s="39"/>
-      <c r="S36" s="40" t="s">
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="16"/>
+      <c r="I35" s="16"/>
+      <c r="J35" s="16"/>
+      <c r="K35" s="16"/>
+      <c r="L35" s="16"/>
+      <c r="M35" s="16"/>
+      <c r="N35" s="16"/>
+      <c r="O35" s="17"/>
+      <c r="P35" s="17"/>
+      <c r="Q35" s="17"/>
+      <c r="R35" s="17"/>
+      <c r="S35" s="17"/>
+      <c r="T35" s="16"/>
+      <c r="U35" s="18"/>
+    </row>
+    <row r="36" spans="1:21" ht="15" thickTop="1">
+      <c r="A36" s="19"/>
+      <c r="B36" s="19"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="19"/>
+      <c r="G36" s="19"/>
+      <c r="H36" s="19"/>
+      <c r="I36" s="19"/>
+      <c r="J36" s="19"/>
+      <c r="K36" s="19"/>
+      <c r="L36" s="19"/>
+      <c r="M36" s="19"/>
+      <c r="N36" s="19"/>
+      <c r="O36" s="19"/>
+      <c r="P36" s="19"/>
+      <c r="Q36" s="19"/>
+      <c r="R36" s="19"/>
+      <c r="S36" s="19"/>
+      <c r="T36" s="19"/>
+      <c r="U36" s="20" t="s">
         <v>27</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="R3:R4"/>
-    <mergeCell ref="S3:S4"/>
+  <mergeCells count="16">
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="D1:N1"/>
+    <mergeCell ref="D2:N2"/>
+    <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:G3"/>
     <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="D1:N1"/>
-    <mergeCell ref="D2:N2"/>
-    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="T3:T4"/>
+    <mergeCell ref="U3:U4"/>
+    <mergeCell ref="R3:S3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>

--- a/public/assets/templates/operasional/mdp.xlsx
+++ b/public/assets/templates/operasional/mdp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\pt_bas\Engineering\public\assets\templates\operasional\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98D5229B-A533-40B3-80D8-59FD83500C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E20C6C-9999-4DEB-AC64-943175B67D08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{48748F47-9D71-4608-BC1F-023F595FFB4F}"/>
   </bookViews>
@@ -114,10 +114,10 @@
     <t>Suhu Ruang</t>
   </si>
   <si>
-    <t>Trafo</t>
-  </si>
-  <si>
-    <t>Genset</t>
+    <t>Trafo (°C)</t>
+  </si>
+  <si>
+    <t>Genset (°C)</t>
   </si>
 </sst>
 </file>
@@ -540,64 +540,64 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -967,22 +967,22 @@
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:21" ht="15" thickTop="1">
-      <c r="A1" s="31"/>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="35" t="s">
+      <c r="A1" s="24"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
       <c r="O1" s="1" t="s">
         <v>1</v>
       </c>
@@ -994,22 +994,22 @@
       <c r="U1" s="4"/>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="33"/>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="37" t="s">
+      <c r="A2" s="26"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
-      <c r="N2" s="38"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
       <c r="O2" s="7" t="s">
         <v>3</v>
       </c>
@@ -1021,59 +1021,59 @@
       <c r="U2" s="10"/>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="24"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="21" t="s">
+      <c r="F3" s="22"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="23" t="s">
+      <c r="I3" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="24"/>
-      <c r="K3" s="30"/>
-      <c r="L3" s="21" t="s">
+      <c r="J3" s="22"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="23" t="s">
+      <c r="M3" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="25" t="s">
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="25"/>
-      <c r="R3" s="25" t="s">
+      <c r="Q3" s="38"/>
+      <c r="R3" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="S3" s="25"/>
-      <c r="T3" s="26" t="s">
+      <c r="S3" s="38"/>
+      <c r="T3" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="U3" s="28" t="s">
+      <c r="U3" s="39" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="26">
-      <c r="A4" s="40"/>
-      <c r="B4" s="27"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
       <c r="E4" s="6" t="s">
         <v>16</v>
       </c>
@@ -1083,7 +1083,7 @@
       <c r="G4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="22"/>
+      <c r="H4" s="37"/>
       <c r="I4" s="6" t="s">
         <v>19</v>
       </c>
@@ -1093,7 +1093,7 @@
       <c r="K4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="L4" s="22"/>
+      <c r="L4" s="37"/>
       <c r="M4" s="6" t="s">
         <v>22</v>
       </c>
@@ -1115,8 +1115,8 @@
       <c r="S4" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="T4" s="27"/>
-      <c r="U4" s="29"/>
+      <c r="T4" s="35"/>
+      <c r="U4" s="40"/>
     </row>
     <row r="5" spans="1:21">
       <c r="A5" s="5">
@@ -1920,6 +1920,10 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="T3:T4"/>
+    <mergeCell ref="U3:U4"/>
+    <mergeCell ref="R3:S3"/>
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="A1:C2"/>
     <mergeCell ref="D1:N1"/>
@@ -1932,10 +1936,6 @@
     <mergeCell ref="H3:H4"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:O3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="T3:T4"/>
-    <mergeCell ref="U3:U4"/>
-    <mergeCell ref="R3:S3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
